--- a/data/trans_bre/P05B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P05B_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>316,21%</t>
+          <t>287,74%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,5</t>
+          <t>-1,59; 2,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,37</t>
+          <t>-0,8; 2,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,19</t>
+          <t>0,22; 4,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,91</t>
+          <t>-0,39; 3,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,5; 173,68</t>
+          <t>-47,34; 189,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,72; 651,85</t>
+          <t>-59,59; 534,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 1579,27</t>
+          <t>-26,19; 1430,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,99</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-43,42%</t>
+          <t>-34,37%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,66</t>
+          <t>-0,66; 3,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,53</t>
+          <t>-1,49; 1,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,2</t>
+          <t>-0,94; 2,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 0,95</t>
+          <t>-3,13; 1,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 160,05</t>
+          <t>-19,64; 155,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,79; 145,19</t>
+          <t>-58,58; 136,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,31; 248,85</t>
+          <t>-43,26; 285,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,49; 97,59</t>
+          <t>-87,07; 171,1</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-25,81%</t>
+          <t>-18,53%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,66</t>
+          <t>0,01; 4,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,64</t>
+          <t>-1,8; 1,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,29</t>
+          <t>-0,33; 2,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,74</t>
+          <t>-1,34; 0,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 190,25</t>
+          <t>-2,02; 180,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 151,06</t>
+          <t>-62,89; 128,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 365,59</t>
+          <t>-32,68; 387,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-84,07; 177,15</t>
+          <t>-83,83; 214,52</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>135,33%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,44</t>
+          <t>0,01; 4,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,65</t>
+          <t>-2,97; 0,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,72</t>
+          <t>-1,41; 1,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,44</t>
+          <t>-0,31; 1,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 406,1</t>
+          <t>-7,14; 423,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,55; 66,55</t>
+          <t>-84,2; 53,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,75; 211,17</t>
+          <t>-60,05; 201,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,69; 1046,72</t>
+          <t>-47,25; 602,78</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 4,1</t>
+          <t>-1,9; 3,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,85</t>
+          <t>-1,44; 1,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,03</t>
+          <t>-1,48; 1,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,18</t>
+          <t>-1,09; 1,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 160,92</t>
+          <t>-40,12; 144,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-72,79; 377,0</t>
+          <t>-73,07; 478,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-67,6; 485,11</t>
+          <t>-78,66; 363,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,08; 150,56</t>
+          <t>-55,89; 176,21</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-20,85%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 7,55</t>
+          <t>2,02; 7,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,51</t>
+          <t>-1,32; 1,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,97</t>
+          <t>-1,04; 2,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,89</t>
+          <t>-1,12; 1,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>79,15; 1761,13</t>
+          <t>68,05; 2114,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,75; 766,72</t>
+          <t>-58,37; 677,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,46; 98,89</t>
+          <t>-54,13; 160,21</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>54,04%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 2,69</t>
+          <t>-4,0; 3,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,81</t>
+          <t>-2,04; 2,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,55</t>
+          <t>-1,9; 3,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,39</t>
+          <t>-0,75; 1,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 101,57</t>
+          <t>-62,61; 128,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-66,33; 502,52</t>
+          <t>-67,8; 415,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 257,81</t>
+          <t>-59,85; 290,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-63,06; 507,93</t>
+          <t>-57,88; 471,09</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,67</t>
+          <t>0,81; 2,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,62</t>
+          <t>-0,66; 0,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,46</t>
+          <t>0,13; 1,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,65</t>
+          <t>-0,35; 0,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,44; 108,36</t>
+          <t>23,25; 101,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 47,56</t>
+          <t>-33,18; 47,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,97; 136,62</t>
+          <t>6,54; 127,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,96; 85,03</t>
+          <t>-26,5; 73,67</t>
         </is>
       </c>
     </row>
